--- a/data/trans_bre/P3A_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R2-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 3,43</t>
+          <t>-5,9; 3,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 3,28</t>
+          <t>-4,97; 3,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 4,23</t>
+          <t>-2,87; 4,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 3,1</t>
+          <t>-2,85; 2,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 34,05</t>
+          <t>-43,97; 37,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-49,86; 50,37</t>
+          <t>-48,77; 45,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 109,26</t>
+          <t>-43,13; 112,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,25; 54,52</t>
+          <t>-33,98; 47,52</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 1,85</t>
+          <t>-4,91; 1,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 4,17</t>
+          <t>-2,86; 4,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,19</t>
+          <t>-2,94; 2,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,54</t>
+          <t>-1,95; 2,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,02; 59,84</t>
+          <t>-66,15; 48,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 140,51</t>
+          <t>-49,08; 135,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,57; 162,75</t>
+          <t>-76,46; 171,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 91,67</t>
+          <t>-37,37; 98,26</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,33</t>
+          <t>-2,27; 3,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,07</t>
+          <t>-0,53; 5,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,28</t>
+          <t>-1,47; 3,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 8,88</t>
+          <t>2,2; 9,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-76,44; 210,06</t>
+          <t>-77,92; 210,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 292,39</t>
+          <t>-28,06; 311,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 453,86</t>
+          <t>-74,85; 446,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,28; 942,43</t>
+          <t>54,99; 858,39</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,44</t>
+          <t>-1,88; 0,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,47</t>
+          <t>-2,22; 0,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,36</t>
+          <t>-1,28; 1,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,43</t>
+          <t>-4,21; -0,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,23; 36,7</t>
+          <t>-76,14; 24,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,76; 29,68</t>
+          <t>-71,76; 42,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 95,71</t>
+          <t>-55,64; 106,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,24; -11,73</t>
+          <t>-71,89; -11,04</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,99</t>
+          <t>-1,02; 2,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 0,68</t>
+          <t>-3,8; 0,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,37</t>
+          <t>-2,39; 0,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,16</t>
+          <t>-0,73; 3,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-59,4; 451,19</t>
+          <t>-61,05; 404,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 25,01</t>
+          <t>-64,44; 22,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-79,41; 29,98</t>
+          <t>-78,69; 37,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 114,88</t>
+          <t>-14,63; 119,81</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 0,25</t>
+          <t>-4,76; 0,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,28</t>
+          <t>1,52; 6,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,8</t>
+          <t>0,13; 4,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 7,64</t>
+          <t>-2,36; 7,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-67,05; 12,09</t>
+          <t>-66,43; 10,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,18; 534,98</t>
+          <t>30,38; 500,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 633,65</t>
+          <t>-3,42; 692,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 1031,78</t>
+          <t>-33,12; 1095,81</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,05</t>
+          <t>-1,78; 0,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,85</t>
+          <t>-0,29; 1,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,44</t>
+          <t>-0,28; 1,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 2,42</t>
+          <t>-0,09; 2,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-40,11; 1,63</t>
+          <t>-39,57; 3,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 56,07</t>
+          <t>-6,47; 51,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 69,39</t>
+          <t>-10,87; 64,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 67,98</t>
+          <t>-1,82; 64,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P3A_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P3A_R2-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 3,35</t>
+          <t>-5,97; 3,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 3,02</t>
+          <t>-5,28; 3,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 4,28</t>
+          <t>-3,15; 4,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 2,69</t>
+          <t>-2,55; 3,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-43,97; 37,37</t>
+          <t>-44,55; 36,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,77; 45,77</t>
+          <t>-48,8; 46,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 112,58</t>
+          <t>-44,99; 117,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 47,52</t>
+          <t>-30,13; 55,11</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 1,41</t>
+          <t>-4,67; 1,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 4,35</t>
+          <t>-2,77; 4,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,11</t>
+          <t>-2,79; 2,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,72</t>
+          <t>-1,49; 3,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-66,15; 48,1</t>
+          <t>-63,92; 58,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 135,36</t>
+          <t>-49,28; 139,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-76,46; 171,37</t>
+          <t>-71,0; 143,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,37; 98,26</t>
+          <t>-28,23; 121,52</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>3,58</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>208,06%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 3,73</t>
+          <t>-2,18; 3,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,4</t>
+          <t>-0,59; 4,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,94</t>
+          <t>-1,56; 3,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,48</t>
+          <t>0,45; 7,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,92; 210,59</t>
+          <t>-74,48; 227,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 311,05</t>
+          <t>-23,99; 337,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-74,85; 446,84</t>
+          <t>-100,0; 401,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54,99; 858,39</t>
+          <t>8,22; 246,23</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,07</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-43,91%</t>
+          <t>-29,91%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,28</t>
+          <t>-1,76; 0,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,65</t>
+          <t>-2,11; 0,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,35</t>
+          <t>-1,23; 1,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,21; -0,35</t>
+          <t>-3,04; 0,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,14; 24,2</t>
+          <t>-70,95; 32,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,76; 42,72</t>
+          <t>-69,48; 45,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-55,64; 106,17</t>
+          <t>-56,71; 102,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,89; -11,04</t>
+          <t>-53,59; 3,52</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>67,0%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,17</t>
+          <t>-1,11; 2,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,56</t>
+          <t>-3,76; 0,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,44</t>
+          <t>-2,53; 0,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,3</t>
+          <t>0,43; 3,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-61,05; 404,47</t>
+          <t>-55,64; 453,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-64,44; 22,09</t>
+          <t>-62,13; 27,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-78,69; 37,12</t>
+          <t>-78,29; 36,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 119,81</t>
+          <t>7,65; 165,84</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,56</t>
+          <t>4,38</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>137,68%</t>
+          <t>135,51%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,29</t>
+          <t>-5,04; 0,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,28</t>
+          <t>1,37; 6,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,6</t>
+          <t>0,26; 4,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 7,52</t>
+          <t>-1,76; 7,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,43; 10,74</t>
+          <t>-66,55; 11,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,38; 500,02</t>
+          <t>24,83; 558,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 692,34</t>
+          <t>-4,96; 690,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 1095,81</t>
+          <t>-22,69; 870,25</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,07</t>
+          <t>-1,88; 0,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,74</t>
+          <t>-0,31; 1,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,36</t>
+          <t>-0,23; 1,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 2,28</t>
+          <t>0,2; 2,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-39,57; 3,22</t>
+          <t>-40,7; 3,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 51,93</t>
+          <t>-7,7; 53,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 64,03</t>
+          <t>-8,69; 72,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 64,93</t>
+          <t>4,37; 53,4</t>
         </is>
       </c>
     </row>
